--- a/data-manipulation-scripts/sheets-cleanup/sheets/JUNTA MAGNETO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/JUNTA MAGNETO.xlsx
@@ -28,25 +28,25 @@
     <t>7899641814731</t>
   </si>
   <si>
-    <t>JUNTA MAG VEDAMOTOS CG TITAN FAN150 2004/ CRF150F 2012/ BROS NXR160 2006</t>
+    <t>JUNTA MAGNETO VEDAMOTOS CG TITAN FAN150 2004/ CRF150F 2012/ BROS NXR160 2006</t>
   </si>
   <si>
     <t>7899641806644</t>
   </si>
   <si>
-    <t>JUNTA MAG VEDAMOTOS YBR125 XTZ125 2011 A 2017</t>
+    <t>JUNTA MAGNETO VEDAMOTOS YBR125 XTZ125 2011 A 2017</t>
   </si>
   <si>
     <t>7899641801441</t>
   </si>
   <si>
-    <t>JUNTA MAG VEDAMOTOS FAN CG125/ TITAN 2000/ NXR BROS125 2003 A 2005</t>
+    <t>JUNTA MAGNETO VEDAMOTOS FAN CG125/ TITAN 2000/ NXR BROS125 2003 A 2005</t>
   </si>
   <si>
     <t>7899641801939</t>
   </si>
   <si>
-    <t>JUNTA MAG VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
+    <t>JUNTA MAGNETO VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
   </si>
   <si>
     <t>7899641805623</t>
@@ -64,31 +64,31 @@
     <t>7895442673959</t>
   </si>
   <si>
-    <t>JUNTA MAG VALFLEX SUSUKI YES125 2002 A 2008 67395</t>
+    <t>JUNTA MAGNETO VALFLEX SUSUKI YES125 2002 A 2008 67395</t>
   </si>
   <si>
     <t>6942234802989</t>
   </si>
   <si>
-    <t>JUNTA MAG BRAVIC FAZER250/ LANDER XTZ250 2016 2019 BMA48507</t>
+    <t>JUNTA MAGNETO BRAVIC FAZER250/ LANDER XTZ250 2016 2019 BMA48507</t>
   </si>
   <si>
     <t>7893986388339</t>
   </si>
   <si>
-    <t>JUNTA MAG PEÇA+ FAZER150/ CROSSER XTZ150/ FACTOR150</t>
+    <t>JUNTA MAGNETO PEÇA+ FAZER150/ CROSSER XTZ150/ FACTOR150</t>
   </si>
   <si>
     <t>7893986440686</t>
   </si>
   <si>
-    <t>JUNTA MAG PEÇA+ TWISTER 2016</t>
+    <t>JUNTA MAGNETO PEÇA+ TWISTER 2016</t>
   </si>
   <si>
     <t>6942234802972</t>
   </si>
   <si>
-    <t>JUNTA MAG BRAVIC FAZER150/ XTZ150 CROSSER 2016 A 2019 BMA48506</t>
+    <t>JUNTA MAGNETO BRAVIC FAZER150/ XTZ150 CROSSER 2016 A 2019 BMA48506</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -143,10 +143,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -413,10 +413,12 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>14.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -447,10 +449,12 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>13.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -481,10 +485,12 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>12.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -512,13 +518,15 @@
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="7">
         <v>9.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -552,7 +560,9 @@
       <c r="C6" s="7">
         <v>4.0</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -586,7 +596,9 @@
       <c r="C7" s="7">
         <v>5.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="4">
+        <v>20.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -614,13 +626,15 @@
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="7">
         <v>1.0</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="4">
+        <v>15.0</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -648,13 +662,15 @@
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="7">
         <v>10.0</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="4">
+        <v>15.0</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -682,7 +698,7 @@
       <c r="A10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="7">
@@ -718,7 +734,7 @@
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="7">
@@ -754,7 +770,7 @@
       <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="7">
